--- a/bills/huixinjiqiren/-5126482759/e06b39ba5a49d2ce7852c0099b7c134e1071c055b5485c16b4aed346922811a5/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5126482759/e06b39ba5a49d2ce7852c0099b7c134e1071c055b5485c16b4aed346922811a5/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/30 08:27:25</t>
+          <t>09/30 19:07:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16049.38</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>dashengfa888999</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,183 +117,225 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>09/30 08:27:25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>130000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>16049.38</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>dashengfa888999</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>09/24 10:56:50</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.25</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>6060.61</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>dashengfa888999</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>180000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>22109.99</t>
+          <t>230000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28359.99</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>22109.99</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>28359.99</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5126482759/e06b39ba5a49d2ce7852c0099b7c134e1071c055b5485c16b4aed346922811a5/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5126482759/e06b39ba5a49d2ce7852c0099b7c134e1071c055b5485c16b4aed346922811a5/bill-all.xlsx
@@ -283,59 +283,86 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>09/30 19:07:19</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>6250</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>230000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>28359.99</t>
+          <t>230000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28359.99</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>6250</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>28359.99</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>22109.99</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5126482759/e06b39ba5a49d2ce7852c0099b7c134e1071c055b5485c16b4aed346922811a5/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5126482759/e06b39ba5a49d2ce7852c0099b7c134e1071c055b5485c16b4aed346922811a5/bill-all.xlsx
@@ -286,83 +286,110 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>09/30 19:07:48</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>16049</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>09/30 19:07:19</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>6250</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>230000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>28359.99</t>
+          <t>230000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>28359.99</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>22299</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>22109.99</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>6060.99</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5126482759/e06b39ba5a49d2ce7852c0099b7c134e1071c055b5485c16b4aed346922811a5/bill-all.xlsx
+++ b/bills/huixinjiqiren/-5126482759/e06b39ba5a49d2ce7852c0099b7c134e1071c055b5485c16b4aed346922811a5/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/30 19:07:00</t>
+          <t>10/20 16:12:26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/30 08:27:25</t>
+          <t>10/16 13:26:11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16049.38</t>
+          <t>17901.23</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>dashengfa888999</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,92 +159,168 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/24 10:56:50</t>
+          <t>10/16 13:25:42</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>145000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>145000</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>dashengfa888999</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>09/30 19:07:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>8.25</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>6060.61</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>dashengfa888999</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>6250</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>代付</t>
+          <t>09/30 08:27:25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>130000</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>16049.38</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>dashengfa888999</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>时间</t>
+          <t>09/24 10:56:50</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>金额</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>费率</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>汇率</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>结算</t>
+          <t>6060.61</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>标记人</t>
+          <t/>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>操作人</t>
+          <t>dashengfa888999</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -252,7 +328,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>下发</t>
+          <t>代付</t>
         </is>
       </c>
     </row>
@@ -269,127 +345,204 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>费率</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>汇率</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>结算</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>09/30 19:07:48</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>16049</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/30 19:07:19</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>6250</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>10/16 13:26:21</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>09/30 19:07:48</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>16049</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>09/30 19:07:19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>28359.99</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>22299</t>
-        </is>
-      </c>
-    </row>
+          <t>6250</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>620000</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>203606.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>37299</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>6060.99</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>166307.9</t>
         </is>
       </c>
     </row>
